--- a/database/event/3376/event_3376_evp_summary.xlsx
+++ b/database/event/3376/event_3376_evp_summary.xlsx
@@ -492,93 +492,93 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5503</v>
+        <v>7.7257</v>
       </c>
       <c r="C2" t="n">
-        <v>3.5299</v>
+        <v>3.6119</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6288</v>
+        <v>2.634</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5503</v>
+        <v>7.7257</v>
       </c>
       <c r="F2" t="n">
-        <v>4.123</v>
+        <v>2.5694</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4273</v>
+        <v>5.1563</v>
       </c>
       <c r="H2" t="n">
-        <v>4.123</v>
+        <v>2.5694</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3418</v>
+        <v>2.5694</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4273</v>
+        <v>5.1563</v>
       </c>
       <c r="K2" t="n">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="L2" t="n">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7691</v>
+        <v>7.7257</v>
       </c>
       <c r="N2" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.8825</v>
+        <v>7.7044</v>
       </c>
       <c r="C3" t="n">
-        <v>3.2177</v>
+        <v>3.6019</v>
       </c>
       <c r="D3" t="n">
-        <v>2.359</v>
+        <v>2.6255</v>
       </c>
       <c r="E3" t="n">
-        <v>6.8825</v>
+        <v>7.7044</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7262</v>
+        <v>4.2771</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1563</v>
+        <v>3.4273</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7262</v>
+        <v>4.6473</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7262</v>
+        <v>3.7668</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1563</v>
+        <v>3.4273</v>
       </c>
       <c r="K3" t="n">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="L3" t="n">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="M3" t="n">
-        <v>6.8825</v>
+        <v>7.1941</v>
       </c>
       <c r="N3" t="n">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4">
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0712</v>
+        <v>6.033</v>
       </c>
       <c r="C4" t="n">
-        <v>2.8384</v>
+        <v>2.8205</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0313</v>
+        <v>1.9596</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0712</v>
+        <v>6.033</v>
       </c>
       <c r="F4" t="n">
-        <v>4.8923</v>
+        <v>4.8541</v>
       </c>
       <c r="G4" t="n">
         <v>1.1789</v>
       </c>
       <c r="H4" t="n">
-        <v>5.368</v>
+        <v>5.3082</v>
       </c>
       <c r="I4" t="n">
         <v>5.4433</v>
@@ -630,127 +630,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>s1mple</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0406</v>
+        <v>5.2107</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3566</v>
+        <v>2.4361</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6149</v>
+        <v>1.632</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0406</v>
+        <v>5.2107</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4214</v>
+        <v>4.0842</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6192</v>
+        <v>1.1265</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4214</v>
+        <v>4.101</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4214</v>
+        <v>4.1704</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6192</v>
+        <v>1.1265</v>
       </c>
       <c r="K5" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="L5" t="n">
-        <v>188</v>
+        <v>42</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0406</v>
+        <v>5.2969</v>
       </c>
       <c r="N5" t="n">
-        <v>308</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>s1mple</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.9635</v>
+        <v>5.0406</v>
       </c>
       <c r="C6" t="n">
-        <v>2.3205</v>
+        <v>2.3566</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5838</v>
+        <v>1.5643</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9635</v>
+        <v>5.0406</v>
       </c>
       <c r="F6" t="n">
-        <v>3.837</v>
+        <v>1.4214</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1265</v>
+        <v>3.6192</v>
       </c>
       <c r="H6" t="n">
-        <v>3.837</v>
+        <v>1.4214</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8728</v>
+        <v>1.4214</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1265</v>
+        <v>3.6192</v>
       </c>
       <c r="K6" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="L6" t="n">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="M6" t="n">
-        <v>4.9993</v>
+        <v>5.0406</v>
       </c>
       <c r="N6" t="n">
-        <v>242</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6708</v>
+        <v>4.7858</v>
       </c>
       <c r="C7" t="n">
-        <v>2.1837</v>
+        <v>2.2374</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4655</v>
+        <v>1.4628</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6708</v>
+        <v>4.7858</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5248</v>
+        <v>2.9587</v>
       </c>
       <c r="G7" t="n">
-        <v>3.146</v>
+        <v>1.8271</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5248</v>
+        <v>2.9587</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2359</v>
+        <v>2.3981</v>
       </c>
       <c r="J7" t="n">
-        <v>3.146</v>
+        <v>1.8271</v>
       </c>
       <c r="K7" t="n">
         <v>149</v>
@@ -759,7 +759,7 @@
         <v>153</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3819</v>
+        <v>4.2252</v>
       </c>
       <c r="N7" t="n">
         <v>302</v>
@@ -768,185 +768,185 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6655</v>
+        <v>4.6708</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1812</v>
+        <v>2.1837</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4634</v>
+        <v>1.4169</v>
       </c>
       <c r="E8" t="n">
-        <v>4.6655</v>
+        <v>4.6708</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7668</v>
+        <v>1.5248</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8987</v>
+        <v>3.146</v>
       </c>
       <c r="H8" t="n">
-        <v>1.7668</v>
+        <v>1.5248</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7668</v>
+        <v>1.2359</v>
       </c>
       <c r="J8" t="n">
-        <v>2.8987</v>
+        <v>3.146</v>
       </c>
       <c r="K8" t="n">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="L8" t="n">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6655</v>
+        <v>4.3819</v>
       </c>
       <c r="N8" t="n">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.4926</v>
+        <v>4.6655</v>
       </c>
       <c r="C9" t="n">
-        <v>2.1004</v>
+        <v>2.1812</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3935</v>
+        <v>1.4148</v>
       </c>
       <c r="E9" t="n">
-        <v>4.4926</v>
+        <v>4.6655</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6953</v>
+        <v>1.7668</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7973</v>
+        <v>2.8987</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6953</v>
+        <v>1.7668</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7471</v>
+        <v>1.7668</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7973</v>
+        <v>2.8987</v>
       </c>
       <c r="K9" t="n">
-        <v>227</v>
+        <v>120</v>
       </c>
       <c r="L9" t="n">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="M9" t="n">
-        <v>4.5444</v>
+        <v>4.6655</v>
       </c>
       <c r="N9" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3025</v>
+        <v>4.4514</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0115</v>
+        <v>2.0811</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3168</v>
+        <v>1.3295</v>
       </c>
       <c r="E10" t="n">
-        <v>4.3025</v>
+        <v>4.4514</v>
       </c>
       <c r="F10" t="n">
-        <v>1.355</v>
+        <v>3.6541</v>
       </c>
       <c r="G10" t="n">
-        <v>2.9475</v>
+        <v>0.7973</v>
       </c>
       <c r="H10" t="n">
-        <v>1.355</v>
+        <v>3.6541</v>
       </c>
       <c r="I10" t="n">
-        <v>1.355</v>
+        <v>3.7471</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9475</v>
+        <v>0.7973</v>
       </c>
       <c r="K10" t="n">
-        <v>115</v>
+        <v>227</v>
       </c>
       <c r="L10" t="n">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3025</v>
+        <v>4.5444</v>
       </c>
       <c r="N10" t="n">
-        <v>239</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.2906</v>
+        <v>4.3276</v>
       </c>
       <c r="C11" t="n">
-        <v>2.0059</v>
+        <v>2.0232</v>
       </c>
       <c r="D11" t="n">
-        <v>1.3119</v>
+        <v>1.2802</v>
       </c>
       <c r="E11" t="n">
-        <v>4.2906</v>
+        <v>4.3276</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4635</v>
+        <v>1.3801</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8271</v>
+        <v>2.9475</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4635</v>
+        <v>1.3801</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9968</v>
+        <v>1.3801</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8271</v>
+        <v>2.9475</v>
       </c>
       <c r="K11" t="n">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="L11" t="n">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8239</v>
+        <v>4.3276</v>
       </c>
       <c r="N11" t="n">
-        <v>302</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
@@ -962,7 +962,7 @@
         <v>1.8754</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1992</v>
+        <v>1.1543</v>
       </c>
       <c r="E12" t="n">
         <v>4.0115</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5899</v>
+        <v>3.5959</v>
       </c>
       <c r="C13" t="n">
-        <v>1.6783</v>
+        <v>1.6811</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0289</v>
+        <v>0.9887</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5899</v>
+        <v>3.5959</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8613</v>
+        <v>1.8403</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2714</v>
+        <v>1.7556</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8613</v>
+        <v>1.8403</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1297</v>
+        <v>1.8403</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2714</v>
+        <v>1.7556</v>
       </c>
       <c r="K13" t="n">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="L13" t="n">
-        <v>153</v>
+        <v>188</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8583</v>
+        <v>3.5959</v>
       </c>
       <c r="N13" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.2526</v>
+        <v>3.5899</v>
       </c>
       <c r="C14" t="n">
-        <v>1.5206</v>
+        <v>1.6783</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.9863</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2526</v>
+        <v>3.5899</v>
       </c>
       <c r="F14" t="n">
-        <v>4.2182</v>
+        <v>3.8613</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.9656</v>
+        <v>-0.2714</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4103</v>
+        <v>3.8613</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5747</v>
+        <v>3.1297</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9656</v>
+        <v>-0.2714</v>
       </c>
       <c r="K14" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="L14" t="n">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6091</v>
+        <v>2.8583</v>
       </c>
       <c r="N14" t="n">
-        <v>194</v>
+        <v>302</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0952</v>
+        <v>3.336</v>
       </c>
       <c r="C15" t="n">
-        <v>1.4471</v>
+        <v>1.5596</v>
       </c>
       <c r="D15" t="n">
-        <v>0.829</v>
+        <v>0.8852</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0952</v>
+        <v>3.336</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3396</v>
+        <v>3.336</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7556</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3396</v>
+        <v>3.336</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3396</v>
+        <v>3.336</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7556</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>120</v>
+        <v>197</v>
       </c>
       <c r="L15" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.0952</v>
+        <v>3.336</v>
       </c>
       <c r="N15" t="n">
-        <v>308</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9927</v>
+        <v>3.2526</v>
       </c>
       <c r="C16" t="n">
-        <v>1.3991</v>
+        <v>1.5206</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7876</v>
+        <v>0.8519</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9927</v>
+        <v>3.2526</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9927</v>
+        <v>4.2182</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.9656</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9927</v>
+        <v>4.4103</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9927</v>
+        <v>3.5747</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.9656</v>
       </c>
       <c r="K16" t="n">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9927</v>
+        <v>2.6091</v>
       </c>
       <c r="N16" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.9486</v>
+        <v>2.9807</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3785</v>
+        <v>1.3935</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7698</v>
+        <v>0.7436</v>
       </c>
       <c r="E17" t="n">
-        <v>2.9486</v>
+        <v>2.9807</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0115</v>
+        <v>3.0436</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0629</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0115</v>
+        <v>3.0436</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4409</v>
+        <v>2.4669</v>
       </c>
       <c r="J17" t="n">
         <v>-0.0629</v>
@@ -1219,7 +1219,7 @@
         <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>2.378</v>
+        <v>2.404</v>
       </c>
       <c r="N17" t="n">
         <v>194</v>
@@ -1228,90 +1228,90 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.7976</v>
+        <v>2.86</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3079</v>
+        <v>1.3371</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7088</v>
+        <v>0.6955</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7976</v>
+        <v>2.86</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2746</v>
+        <v>3.86</v>
       </c>
       <c r="G18" t="n">
-        <v>0.523</v>
+        <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>2.2746</v>
+        <v>3.86</v>
       </c>
       <c r="I18" t="n">
-        <v>2.2746</v>
+        <v>3.1286</v>
       </c>
       <c r="J18" t="n">
-        <v>0.523</v>
+        <v>-1</v>
       </c>
       <c r="K18" t="n">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="L18" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="M18" t="n">
-        <v>2.7976</v>
+        <v>2.1286</v>
       </c>
       <c r="N18" t="n">
-        <v>239</v>
+        <v>194</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Subroza</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.6766</v>
+        <v>2.8458</v>
       </c>
       <c r="C19" t="n">
-        <v>1.2514</v>
+        <v>1.3305</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6599</v>
+        <v>0.6899</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6766</v>
+        <v>2.8458</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6766</v>
+        <v>3.3818</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.536</v>
       </c>
       <c r="H19" t="n">
-        <v>2.6766</v>
+        <v>3.3818</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7016</v>
+        <v>3.439</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.536</v>
       </c>
       <c r="K19" t="n">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M19" t="n">
-        <v>2.7016</v>
+        <v>2.903</v>
       </c>
       <c r="N19" t="n">
         <v>242</v>
@@ -1320,354 +1320,354 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.673</v>
+        <v>2.7976</v>
       </c>
       <c r="C20" t="n">
-        <v>1.2497</v>
+        <v>1.3079</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6585</v>
+        <v>0.6707</v>
       </c>
       <c r="E20" t="n">
-        <v>2.673</v>
+        <v>2.7976</v>
       </c>
       <c r="F20" t="n">
-        <v>3.209</v>
+        <v>2.2746</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.536</v>
+        <v>0.523</v>
       </c>
       <c r="H20" t="n">
-        <v>3.209</v>
+        <v>2.2746</v>
       </c>
       <c r="I20" t="n">
-        <v>3.239</v>
+        <v>2.2746</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.536</v>
+        <v>0.523</v>
       </c>
       <c r="K20" t="n">
-        <v>200</v>
+        <v>115</v>
       </c>
       <c r="L20" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="M20" t="n">
-        <v>2.703</v>
+        <v>2.7976</v>
       </c>
       <c r="N20" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gratisfaction</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.6693</v>
+        <v>2.732</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2479</v>
+        <v>1.2773</v>
       </c>
       <c r="D21" t="n">
-        <v>0.657</v>
+        <v>0.6445</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6693</v>
+        <v>2.732</v>
       </c>
       <c r="F21" t="n">
-        <v>3.027</v>
+        <v>3.3464</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3577</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>3.027</v>
+        <v>3.3464</v>
       </c>
       <c r="I21" t="n">
-        <v>3.0694</v>
+        <v>2.7123</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3577</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>227</v>
+        <v>152</v>
       </c>
       <c r="L21" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7117</v>
+        <v>2.0979</v>
       </c>
       <c r="N21" t="n">
-        <v>302</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>Subroza</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6007</v>
+        <v>2.6567</v>
       </c>
       <c r="C22" t="n">
-        <v>1.2159</v>
+        <v>1.2421</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6293</v>
+        <v>0.6145</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6007</v>
+        <v>2.6567</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1268</v>
+        <v>2.6567</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4739</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1268</v>
+        <v>2.6567</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1567</v>
+        <v>2.7016</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4739</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="L22" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.6306</v>
+        <v>2.7016</v>
       </c>
       <c r="N22" t="n">
-        <v>302</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Gratisfaction</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.2948</v>
+        <v>2.6355</v>
       </c>
       <c r="C23" t="n">
-        <v>1.0729</v>
+        <v>1.2321</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5057</v>
+        <v>0.6061</v>
       </c>
       <c r="E23" t="n">
-        <v>2.2948</v>
+        <v>2.6355</v>
       </c>
       <c r="F23" t="n">
-        <v>3.2948</v>
+        <v>2.9932</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>-0.3577</v>
       </c>
       <c r="H23" t="n">
-        <v>3.2948</v>
+        <v>2.9932</v>
       </c>
       <c r="I23" t="n">
-        <v>2.6705</v>
+        <v>3.0694</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>-0.3577</v>
       </c>
       <c r="K23" t="n">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="L23" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="M23" t="n">
-        <v>1.6705</v>
+        <v>2.7117</v>
       </c>
       <c r="N23" t="n">
-        <v>194</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.2239</v>
+        <v>2.577</v>
       </c>
       <c r="C24" t="n">
-        <v>1.0397</v>
+        <v>1.2048</v>
       </c>
       <c r="D24" t="n">
-        <v>0.477</v>
+        <v>0.5828</v>
       </c>
       <c r="E24" t="n">
-        <v>2.2239</v>
+        <v>2.577</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8383</v>
+        <v>2.1031</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6143999999999999</v>
+        <v>0.4739</v>
       </c>
       <c r="H24" t="n">
-        <v>2.8383</v>
+        <v>2.1031</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3005</v>
+        <v>2.1567</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6143999999999999</v>
+        <v>0.4739</v>
       </c>
       <c r="K24" t="n">
-        <v>152</v>
+        <v>227</v>
       </c>
       <c r="L24" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6861</v>
+        <v>2.6306</v>
       </c>
       <c r="N24" t="n">
-        <v>194</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.0754</v>
+        <v>2.3285</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9703000000000001</v>
+        <v>1.0886</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4171</v>
+        <v>0.4838</v>
       </c>
       <c r="E25" t="n">
-        <v>2.0754</v>
+        <v>2.3285</v>
       </c>
       <c r="F25" t="n">
-        <v>2.0754</v>
+        <v>2.8325</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.504</v>
       </c>
       <c r="H25" t="n">
-        <v>2.0754</v>
+        <v>2.8325</v>
       </c>
       <c r="I25" t="n">
-        <v>2.0948</v>
+        <v>2.2958</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.504</v>
       </c>
       <c r="K25" t="n">
-        <v>242</v>
+        <v>152</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>2.0948</v>
+        <v>1.7918</v>
       </c>
       <c r="N25" t="n">
-        <v>242</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>ISSAA</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.9526</v>
+        <v>2.1207</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9129</v>
+        <v>0.9915</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3674</v>
+        <v>0.401</v>
       </c>
       <c r="E26" t="n">
-        <v>1.9526</v>
+        <v>2.1207</v>
       </c>
       <c r="F26" t="n">
-        <v>2.4566</v>
+        <v>2.1207</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.504</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.4566</v>
+        <v>2.1207</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9911</v>
+        <v>2.1207</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.504</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="L26" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4871</v>
+        <v>2.1207</v>
       </c>
       <c r="N26" t="n">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WARDELL</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.8874</v>
+        <v>2.06</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8824</v>
+        <v>0.9631</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3411</v>
+        <v>0.3768</v>
       </c>
       <c r="E27" t="n">
-        <v>1.8874</v>
+        <v>2.06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8874</v>
+        <v>2.06</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.8874</v>
+        <v>2.06</v>
       </c>
       <c r="I27" t="n">
-        <v>1.905</v>
+        <v>2.0948</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.905</v>
+        <v>2.0948</v>
       </c>
       <c r="N27" t="n">
         <v>242</v>
@@ -1688,124 +1688,124 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>WARDELL</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.608</v>
+        <v>1.8733</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7518</v>
+        <v>0.8758</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2282</v>
+        <v>0.3024</v>
       </c>
       <c r="E28" t="n">
-        <v>1.608</v>
+        <v>1.8733</v>
       </c>
       <c r="F28" t="n">
-        <v>1.608</v>
+        <v>1.8733</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.608</v>
+        <v>1.8733</v>
       </c>
       <c r="I28" t="n">
-        <v>1.623</v>
+        <v>1.905</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.623</v>
+        <v>1.905</v>
       </c>
       <c r="N28" t="n">
-        <v>268</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ISSAA</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5793</v>
+        <v>1.5999</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.748</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2166</v>
+        <v>0.1935</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5793</v>
+        <v>1.5999</v>
       </c>
       <c r="F29" t="n">
-        <v>1.5793</v>
+        <v>2.8707</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-1.2708</v>
       </c>
       <c r="H29" t="n">
-        <v>1.5793</v>
+        <v>2.8707</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5793</v>
+        <v>2.8707</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-1.2708</v>
       </c>
       <c r="K29" t="n">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M29" t="n">
-        <v>1.5793</v>
+        <v>1.5999</v>
       </c>
       <c r="N29" t="n">
-        <v>173</v>
+        <v>239</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.2813</v>
+        <v>1.596</v>
       </c>
       <c r="C30" t="n">
-        <v>0.599</v>
+        <v>0.7462</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0963</v>
+        <v>0.1919</v>
       </c>
       <c r="E30" t="n">
-        <v>1.2813</v>
+        <v>1.596</v>
       </c>
       <c r="F30" t="n">
-        <v>1.2813</v>
+        <v>1.596</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.2813</v>
+        <v>1.596</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2933</v>
+        <v>1.623</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.2933</v>
+        <v>1.623</v>
       </c>
       <c r="N30" t="n">
         <v>268</v>
@@ -1826,185 +1826,185 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.2245</v>
+        <v>1.2718</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5725</v>
+        <v>0.5946</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0733</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>1.2245</v>
+        <v>1.2718</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0514</v>
+        <v>1.2718</v>
       </c>
       <c r="G31" t="n">
-        <v>1.1731</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0514</v>
+        <v>1.2718</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0514</v>
+        <v>1.2933</v>
       </c>
       <c r="J31" t="n">
-        <v>1.1731</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>120</v>
+        <v>268</v>
       </c>
       <c r="L31" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.2245</v>
+        <v>1.2933</v>
       </c>
       <c r="N31" t="n">
-        <v>308</v>
+        <v>268</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.1956</v>
+        <v>1.2245</v>
       </c>
       <c r="C32" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5725</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0616</v>
+        <v>0.0439</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1956</v>
+        <v>1.2245</v>
       </c>
       <c r="F32" t="n">
-        <v>1.1956</v>
+        <v>0.0514</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.1731</v>
       </c>
       <c r="H32" t="n">
-        <v>1.1956</v>
+        <v>0.0514</v>
       </c>
       <c r="I32" t="n">
-        <v>1.1956</v>
+        <v>0.0514</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1.1731</v>
       </c>
       <c r="K32" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1956</v>
+        <v>1.2245</v>
       </c>
       <c r="N32" t="n">
-        <v>112</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9431</v>
+        <v>1.1956</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4409</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.0404</v>
+        <v>0.0324</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9431</v>
+        <v>1.1956</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9431</v>
+        <v>1.1956</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9431</v>
+        <v>1.1956</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9519</v>
+        <v>1.1956</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>268</v>
+        <v>112</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9519</v>
+        <v>1.1956</v>
       </c>
       <c r="N33" t="n">
-        <v>268</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8722</v>
+        <v>0.9361</v>
       </c>
       <c r="C34" t="n">
-        <v>0.4078</v>
+        <v>0.4376</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8722</v>
+        <v>0.9361</v>
       </c>
       <c r="F34" t="n">
-        <v>2.143</v>
+        <v>0.9361</v>
       </c>
       <c r="G34" t="n">
-        <v>-1.2708</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.143</v>
+        <v>0.9361</v>
       </c>
       <c r="I34" t="n">
-        <v>2.143</v>
+        <v>0.9519</v>
       </c>
       <c r="J34" t="n">
-        <v>-1.2708</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>115</v>
+        <v>268</v>
       </c>
       <c r="L34" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8721999999999999</v>
+        <v>0.9519</v>
       </c>
       <c r="N34" t="n">
-        <v>239</v>
+        <v>268</v>
       </c>
     </row>
     <row r="35">
@@ -2020,7 +2020,7 @@
         <v>0.4054</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.0984</v>
       </c>
       <c r="E35" t="n">
         <v>0.8672</v>
@@ -2060,25 +2060,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8364</v>
+        <v>0.8266</v>
       </c>
       <c r="C36" t="n">
-        <v>0.391</v>
+        <v>0.3865</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0835</v>
+        <v>-0.1146</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8364</v>
+        <v>0.8266</v>
       </c>
       <c r="F36" t="n">
-        <v>0.875</v>
+        <v>0.8652</v>
       </c>
       <c r="G36" t="n">
         <v>-0.0386</v>
       </c>
       <c r="H36" t="n">
-        <v>0.875</v>
+        <v>0.8652</v>
       </c>
       <c r="I36" t="n">
         <v>0.8873</v>
@@ -2106,25 +2106,25 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7766</v>
       </c>
       <c r="C37" t="n">
-        <v>0.3674</v>
+        <v>0.3631</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1039</v>
+        <v>-0.1345</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7766</v>
       </c>
       <c r="F37" t="n">
-        <v>1.2249</v>
+        <v>1.2157</v>
       </c>
       <c r="G37" t="n">
         <v>-0.4391</v>
       </c>
       <c r="H37" t="n">
-        <v>1.2249</v>
+        <v>1.2157</v>
       </c>
       <c r="I37" t="n">
         <v>1.2363</v>
@@ -2148,369 +2148,369 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>ANGE1</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6175</v>
+        <v>0.7493</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2887</v>
+        <v>0.3503</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1719</v>
+        <v>-0.1454</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6175</v>
+        <v>0.7493</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6175</v>
+        <v>0.7493</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6175</v>
+        <v>0.7493</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6175</v>
+        <v>0.7493</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.6175</v>
+        <v>0.7493</v>
       </c>
       <c r="N38" t="n">
-        <v>197</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>emagine</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5831</v>
+        <v>0.6175</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2726</v>
+        <v>0.2887</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1858</v>
+        <v>-0.1979</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5831</v>
+        <v>0.6175</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5831</v>
+        <v>0.6175</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5831</v>
+        <v>0.6175</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5831</v>
+        <v>0.6175</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.5831</v>
+        <v>0.6175</v>
       </c>
       <c r="N39" t="n">
-        <v>81</v>
+        <v>197</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>emagine</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.518</v>
+        <v>0.5831</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2422</v>
+        <v>0.2726</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2121</v>
+        <v>-0.2116</v>
       </c>
       <c r="E40" t="n">
-        <v>0.518</v>
+        <v>0.5831</v>
       </c>
       <c r="F40" t="n">
-        <v>0.518</v>
+        <v>0.5831</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.518</v>
+        <v>0.5831</v>
       </c>
       <c r="I40" t="n">
-        <v>0.518</v>
+        <v>0.5831</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.518</v>
+        <v>0.5831</v>
       </c>
       <c r="N40" t="n">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4888</v>
+        <v>0.518</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2285</v>
+        <v>0.2422</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2239</v>
+        <v>-0.2375</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4888</v>
+        <v>0.518</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4888</v>
+        <v>0.518</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4888</v>
+        <v>0.518</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4888</v>
+        <v>0.518</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4888</v>
+        <v>0.518</v>
       </c>
       <c r="N41" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4299</v>
+        <v>0.4888</v>
       </c>
       <c r="C42" t="n">
-        <v>0.201</v>
+        <v>0.2285</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2477</v>
+        <v>-0.2492</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4299</v>
+        <v>0.4888</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4299</v>
+        <v>0.4888</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4299</v>
+        <v>0.4888</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4299</v>
+        <v>0.4888</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>197</v>
+        <v>105</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0.4299</v>
+        <v>0.4888</v>
       </c>
       <c r="N42" t="n">
-        <v>197</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3956</v>
+        <v>0.4299</v>
       </c>
       <c r="C43" t="n">
-        <v>0.185</v>
+        <v>0.201</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2615</v>
+        <v>-0.2726</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3956</v>
+        <v>0.4299</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3956</v>
+        <v>0.4299</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3956</v>
+        <v>0.4299</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3956</v>
+        <v>0.4299</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3956</v>
+        <v>0.4299</v>
       </c>
       <c r="N43" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>xand</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3715</v>
+        <v>0.3956</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1737</v>
+        <v>0.185</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2713</v>
+        <v>-0.2863</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3715</v>
+        <v>0.3956</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3715</v>
+        <v>0.3956</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3715</v>
+        <v>0.3956</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3715</v>
+        <v>0.3956</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.3715</v>
+        <v>0.3956</v>
       </c>
       <c r="N44" t="n">
-        <v>112</v>
+        <v>173</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ANGE1</t>
+          <t>xand</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2607</v>
+        <v>0.3715</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1219</v>
+        <v>0.1737</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.316</v>
+        <v>-0.2959</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2607</v>
+        <v>0.3715</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2607</v>
+        <v>0.3715</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2607</v>
+        <v>0.3715</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2607</v>
+        <v>0.3715</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2607</v>
+        <v>0.3715</v>
       </c>
       <c r="N45" t="n">
-        <v>173</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46">
@@ -2520,25 +2520,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.2298</v>
+        <v>0.228</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1074</v>
+        <v>0.1066</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3285</v>
+        <v>-0.3531</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2298</v>
+        <v>0.228</v>
       </c>
       <c r="F46" t="n">
-        <v>0.2298</v>
+        <v>0.228</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.2298</v>
+        <v>0.228</v>
       </c>
       <c r="I46" t="n">
         <v>0.2319</v>
@@ -2572,7 +2572,7 @@
         <v>0.0833</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3494</v>
+        <v>-0.3729</v>
       </c>
       <c r="E47" t="n">
         <v>0.1782</v>
@@ -2618,7 +2618,7 @@
         <v>0.0401</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3867</v>
+        <v>-0.4097</v>
       </c>
       <c r="E48" t="n">
         <v>0.0858</v>
@@ -2664,7 +2664,7 @@
         <v>0.0001</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4213</v>
+        <v>-0.4438</v>
       </c>
       <c r="E49" t="n">
         <v>0.0002</v>
@@ -2710,7 +2710,7 @@
         <v>-0.0314</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.4485</v>
+        <v>-0.4707</v>
       </c>
       <c r="E50" t="n">
         <v>-0.0672</v>
@@ -2746,185 +2746,185 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.1505</v>
+        <v>-0.1247</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0704</v>
+        <v>-0.0583</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.4822</v>
+        <v>-0.4936</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.1505</v>
+        <v>-0.1247</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6709000000000001</v>
+        <v>1.8753</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.8214</v>
+        <v>-2</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6709000000000001</v>
+        <v>1.8753</v>
       </c>
       <c r="I51" t="n">
-        <v>0.6771</v>
+        <v>1.8753</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.8214</v>
+        <v>-2</v>
       </c>
       <c r="K51" t="n">
-        <v>200</v>
+        <v>115</v>
       </c>
       <c r="L51" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.1443</v>
+        <v>-0.1247</v>
       </c>
       <c r="N51" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jnt</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.2094</v>
+        <v>-0.1555</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0979</v>
+        <v>-0.0727</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.506</v>
+        <v>-0.5059</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.2094</v>
+        <v>-0.1555</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.2094</v>
+        <v>0.6659</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.8214</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.2094</v>
+        <v>0.6659</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.2094</v>
+        <v>0.6771</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.8214</v>
       </c>
       <c r="K52" t="n">
-        <v>105</v>
+        <v>200</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.2094</v>
+        <v>-0.1443</v>
       </c>
       <c r="N52" t="n">
-        <v>105</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>jnt</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.2721</v>
+        <v>-0.2094</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.1272</v>
+        <v>-0.0979</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5313</v>
+        <v>-0.5273</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2721</v>
+        <v>-0.2094</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.2721</v>
+        <v>-0.2094</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2721</v>
+        <v>-0.2094</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2721</v>
+        <v>-0.2094</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.2721</v>
+        <v>-0.2094</v>
       </c>
       <c r="N53" t="n">
-        <v>72</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.2746</v>
+        <v>-0.2721</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.1284</v>
+        <v>-0.1272</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5323</v>
+        <v>-0.5523</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.2746</v>
+        <v>-0.2721</v>
       </c>
       <c r="F54" t="n">
-        <v>1.7254</v>
+        <v>-0.2721</v>
       </c>
       <c r="G54" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1.7254</v>
+        <v>-0.2721</v>
       </c>
       <c r="I54" t="n">
-        <v>1.7254</v>
+        <v>-0.2721</v>
       </c>
       <c r="J54" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="L54" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.2746</v>
+        <v>-0.2721</v>
       </c>
       <c r="N54" t="n">
-        <v>239</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55">
@@ -2940,7 +2940,7 @@
         <v>-0.1293</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5331</v>
+        <v>-0.5541</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2765</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1819</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5786</v>
+        <v>-0.5989</v>
       </c>
       <c r="E56" t="n">
         <v>-0.3891</v>
@@ -3022,216 +3022,216 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.4236</v>
+        <v>-0.4155</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.198</v>
+        <v>-0.1943</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5925</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4236</v>
+        <v>-0.4155</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.4236</v>
+        <v>-0.4155</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.4236</v>
+        <v>-0.4155</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.4276</v>
+        <v>-0.4155</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>242</v>
+        <v>144</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.4276</v>
+        <v>-0.4155</v>
       </c>
       <c r="N57" t="n">
-        <v>242</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4461</v>
+        <v>-0.4205</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2086</v>
+        <v>-0.1966</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6016</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4461</v>
+        <v>-0.4205</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4461</v>
+        <v>-0.4205</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4461</v>
+        <v>-0.4205</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4461</v>
+        <v>-0.4276</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>72</v>
+        <v>242</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.4461</v>
+        <v>-0.4276</v>
       </c>
       <c r="N58" t="n">
-        <v>72</v>
+        <v>242</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4649</v>
+        <v>-0.4461</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2173</v>
+        <v>-0.2086</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6092</v>
+        <v>-0.6216</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4649</v>
+        <v>-0.4461</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.4649</v>
+        <v>-0.4461</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.4649</v>
+        <v>-0.4461</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4649</v>
+        <v>-0.4461</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.4649</v>
+        <v>-0.4461</v>
       </c>
       <c r="N59" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.4788</v>
+        <v>-0.4649</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.2238</v>
+        <v>-0.2173</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6148</v>
+        <v>-0.6291</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.4788</v>
+        <v>-0.4649</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.4788</v>
+        <v>-0.4649</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.4788</v>
+        <v>-0.4649</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.4788</v>
+        <v>-0.4649</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.4788</v>
+        <v>-0.4649</v>
       </c>
       <c r="N60" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.5226</v>
+        <v>-0.4788</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.2443</v>
+        <v>-0.2238</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6325</v>
+        <v>-0.6347</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.5226</v>
+        <v>-0.4788</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5226</v>
+        <v>-0.4788</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5226</v>
+        <v>-0.4788</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5226</v>
+        <v>-0.4788</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.5226</v>
+        <v>-0.4788</v>
       </c>
       <c r="N61" t="n">
         <v>72</v>
@@ -3252,32 +3252,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.5968</v>
+        <v>-0.5226</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.279</v>
+        <v>-0.2443</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6625</v>
+        <v>-0.6521</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.5968</v>
+        <v>-0.5226</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.5968</v>
+        <v>-0.5226</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.5968</v>
+        <v>-0.5226</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.5968</v>
+        <v>-0.5226</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.5968</v>
+        <v>-0.5226</v>
       </c>
       <c r="N62" t="n">
         <v>72</v>
@@ -3298,170 +3298,170 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.6979</v>
+        <v>-0.5968</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.3263</v>
+        <v>-0.279</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7033</v>
+        <v>-0.6817</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.6979</v>
+        <v>-0.5968</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.6979</v>
+        <v>-0.5968</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.6979</v>
+        <v>-0.5968</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.6979</v>
+        <v>-0.5968</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.6979</v>
+        <v>-0.5968</v>
       </c>
       <c r="N63" t="n">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.7209</v>
+        <v>-0.6979</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.337</v>
+        <v>-0.3263</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7126</v>
+        <v>-0.722</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.7209</v>
+        <v>-0.6979</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.7209</v>
+        <v>-0.6979</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.7209</v>
+        <v>-0.6979</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.7209</v>
+        <v>-0.6979</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.7209</v>
+        <v>-0.6979</v>
       </c>
       <c r="N64" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>aumaN</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8736</v>
+        <v>-0.7209</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4084</v>
+        <v>-0.337</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.7743</v>
+        <v>-0.7311</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8736</v>
+        <v>-0.7209</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8736</v>
+        <v>-0.7209</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8736</v>
+        <v>-0.7209</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8736</v>
+        <v>-0.7209</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.8736</v>
+        <v>-0.7209</v>
       </c>
       <c r="N65" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kaze</t>
+          <t>aumaN</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.087</v>
+        <v>-0.8736</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5082</v>
+        <v>-0.4084</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8605</v>
+        <v>-0.792</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.087</v>
+        <v>-0.8736</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.087</v>
+        <v>-0.8736</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.087</v>
+        <v>-0.8736</v>
       </c>
       <c r="I66" t="n">
-        <v>-1.087</v>
+        <v>-0.8736</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.087</v>
+        <v>-0.8736</v>
       </c>
       <c r="N66" t="n">
         <v>77</v>
@@ -3482,507 +3482,507 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>kaze</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.1486</v>
+        <v>-1.087</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.537</v>
+        <v>-0.5082</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8854</v>
+        <v>-0.877</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.1486</v>
+        <v>-1.087</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.1486</v>
+        <v>-1.087</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.1486</v>
+        <v>-1.087</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.1486</v>
+        <v>-1.087</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-1.1486</v>
+        <v>-1.087</v>
       </c>
       <c r="N67" t="n">
-        <v>144</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.1703</v>
+        <v>-1.1189</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5471</v>
+        <v>-0.5231</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8941</v>
+        <v>-0.8897</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.1703</v>
+        <v>-1.1189</v>
       </c>
       <c r="F68" t="n">
-        <v>-1.1703</v>
+        <v>-1.1189</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-1.1703</v>
+        <v>-1.1189</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.1703</v>
+        <v>-1.1189</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-1.1703</v>
+        <v>-1.1189</v>
       </c>
       <c r="N68" t="n">
-        <v>105</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>advent</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.2499</v>
+        <v>-1.1703</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5844</v>
+        <v>-0.5471</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9263</v>
+        <v>-0.9102</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.2499</v>
+        <v>-1.1703</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.2499</v>
+        <v>-1.1703</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.2499</v>
+        <v>-1.1703</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.2499</v>
+        <v>-1.1703</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-1.2499</v>
+        <v>-1.1703</v>
       </c>
       <c r="N69" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.2561</v>
+        <v>-1.1809</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.5521</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9288</v>
+        <v>-0.9144</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.2561</v>
+        <v>-1.1809</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.2561</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.2561</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.2561</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="K70" t="n">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.2561</v>
+        <v>-1.1809</v>
       </c>
       <c r="N70" t="n">
-        <v>144</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DeadFox</t>
+          <t>advent</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.2567</v>
+        <v>-1.2499</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.5875</v>
+        <v>-0.5844</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.929</v>
+        <v>-0.9419</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.2567</v>
+        <v>-1.2499</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.2567</v>
+        <v>-1.2499</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.2567</v>
+        <v>-1.2499</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.2567</v>
+        <v>-1.2499</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.2567</v>
+        <v>-1.2499</v>
       </c>
       <c r="N71" t="n">
-        <v>173</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>DeadFox</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.3021</v>
+        <v>-1.2567</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.6088</v>
+        <v>-0.5875</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9474</v>
+        <v>-0.9446</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.3021</v>
+        <v>-1.2567</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.3021</v>
+        <v>-1.2567</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.3021</v>
+        <v>-1.2567</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.3021</v>
+        <v>-1.2567</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>144</v>
+        <v>173</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.3021</v>
+        <v>-1.2567</v>
       </c>
       <c r="N72" t="n">
-        <v>144</v>
+        <v>173</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>horvy</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.3086</v>
+        <v>-1.3021</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.6118</v>
+        <v>-0.6088</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.95</v>
+        <v>-0.9627</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.3086</v>
+        <v>-1.3021</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.3086</v>
+        <v>-1.3021</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.3086</v>
+        <v>-1.3021</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.3086</v>
+        <v>-1.3021</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.3086</v>
+        <v>-1.3021</v>
       </c>
       <c r="N73" t="n">
-        <v>112</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>zeph</t>
+          <t>horvy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.338</v>
+        <v>-1.3086</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.6118</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9619</v>
+        <v>-0.9653</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.338</v>
+        <v>-1.3086</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.338</v>
+        <v>-1.3086</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.338</v>
+        <v>-1.3086</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.338</v>
+        <v>-1.3086</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.338</v>
+        <v>-1.3086</v>
       </c>
       <c r="N74" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>zeph</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.3672</v>
+        <v>-1.338</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6392</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9737</v>
+        <v>-0.977</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.3672</v>
+        <v>-1.338</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.3672</v>
+        <v>-1.338</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.3672</v>
+        <v>-1.338</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.3672</v>
+        <v>-1.338</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>144</v>
+        <v>81</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.3672</v>
+        <v>-1.338</v>
       </c>
       <c r="N75" t="n">
-        <v>144</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.4531</v>
+        <v>-1.3672</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.6794</v>
+        <v>-0.6392</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0084</v>
+        <v>-0.9886</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.4531</v>
+        <v>-1.3672</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.4531</v>
+        <v>-1.3672</v>
       </c>
       <c r="G76" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.4531</v>
+        <v>-1.3672</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4573</v>
+        <v>-1.3672</v>
       </c>
       <c r="J76" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="L76" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.4573</v>
+        <v>-1.3672</v>
       </c>
       <c r="N76" t="n">
-        <v>242</v>
+        <v>144</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.4901</v>
+        <v>-1.4497</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.6966</v>
+        <v>-0.6778</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.0233</v>
+        <v>-1.0215</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.4901</v>
+        <v>-1.4497</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5099</v>
+        <v>-0.4497</v>
       </c>
       <c r="G77" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H77" t="n">
-        <v>0.5099</v>
+        <v>-0.4497</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5099</v>
+        <v>-0.4573</v>
       </c>
       <c r="J77" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="K77" t="n">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="L77" t="n">
-        <v>124</v>
+        <v>42</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.4901</v>
+        <v>-1.4573</v>
       </c>
       <c r="N77" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="78">
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.6535</v>
+        <v>-1.6412</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.773</v>
+        <v>-0.7673</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.0893</v>
+        <v>-1.0978</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.6535</v>
+        <v>-1.6412</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.6535</v>
+        <v>-1.6412</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.6535</v>
+        <v>-1.6412</v>
       </c>
       <c r="I78" t="n">
         <v>-1.6689</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.6889</v>
+        <v>-1.6764</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.7896</v>
+        <v>-0.7837</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.1036</v>
+        <v>-1.1118</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.6889</v>
+        <v>-1.6764</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.6889</v>
+        <v>-1.6764</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.6889</v>
+        <v>-1.6764</v>
       </c>
       <c r="I79" t="n">
         <v>-1.7047</v>
@@ -4090,7 +4090,7 @@
         <v>-0.8338</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.1419</v>
+        <v>-1.1545</v>
       </c>
       <c r="E80" t="n">
         <v>-1.7835</v>
@@ -4136,7 +4136,7 @@
         <v>-0.9175</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.2142</v>
+        <v>-1.2258</v>
       </c>
       <c r="E81" t="n">
         <v>-1.9625</v>
